--- a/resources/vaccine_coverage_hun.xlsx
+++ b/resources/vaccine_coverage_hun.xlsx
@@ -8,29 +8,44 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CSURITA\PycharmProjects\PythonProject\counterfactual-analysis-vzv\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12CF1C01-83E8-4589-A552-F0F3590BD02C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5214EEE-8698-40DB-A8AC-6DD2FB51E7AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="vaccines" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Year</t>
   </si>
   <si>
-    <t>Cases</t>
+    <t>1st dose</t>
+  </si>
+  <si>
+    <t>2nd dose</t>
   </si>
 </sst>
 </file>
@@ -83,6 +98,303 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="births"/>
+      <sheetName val="weekly_data"/>
+      <sheetName val="weekly_rates"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="25">
+          <cell r="B25">
+            <v>85225</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="B26">
+            <v>77511</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2">
+        <row r="2">
+          <cell r="B2">
+            <v>1.8914295352143218E-2</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>1.9275715008553598E-2</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="B4">
+            <v>1.8793822133339758E-2</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="B5">
+            <v>1.8842011420861143E-2</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="B6">
+            <v>1.9058863214707372E-2</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7">
+            <v>1.8962484639664604E-2</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="B8">
+            <v>1.8842011420861143E-2</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="B9">
+            <v>1.9131147145989447E-2</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="B10">
+            <v>1.9119099824109101E-2</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11">
+            <v>1.885405874274149E-2</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="B12">
+            <v>1.8299881936245571E-2</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="B13">
+            <v>1.8685396236416643E-2</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="B14">
+            <v>1.8058935498638653E-2</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="B15">
+            <v>1.7263812254535816E-2</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="B16">
+            <v>1.7468616726501698E-2</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="B17">
+            <v>1.7842083704792424E-2</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="B18">
+            <v>1.8275787292484882E-2</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="B19">
+            <v>1.8095077464279692E-2</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="B20">
+            <v>1.8589017661373875E-2</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="B21">
+            <v>1.8781774811459411E-2</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="B22">
+            <v>1.8299881936245571E-2</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23">
+            <v>1.8842011420861143E-2</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="B24">
+            <v>1.8902248030262872E-2</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="B25">
+            <v>1.9420282871117751E-2</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="B26">
+            <v>2.0564778449750621E-2</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="B27">
+            <v>2.0468399874707853E-2</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="B28">
+            <v>2.0456352552827507E-2</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="B29">
+            <v>2.0745488277955811E-2</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="B30">
+            <v>2.0878008818639618E-2</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="B31">
+            <v>2.0817772209237886E-2</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="B32">
+            <v>2.0661157024793389E-2</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="B33">
+            <v>2.0600920415391657E-2</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="B34">
+            <v>2.0384068621545431E-2</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="B35">
+            <v>1.9950365033852974E-2</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="B36">
+            <v>1.9866033780690552E-2</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="B37">
+            <v>2.0347926655904392E-2</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="B38">
+            <v>2.0528636484109582E-2</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="B39">
+            <v>2.0805724887357539E-2</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="B40">
+            <v>2.0805724887357539E-2</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="B41">
+            <v>1.9926270390092281E-2</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="B42">
+            <v>1.9576898055562248E-2</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="B43">
+            <v>1.8938389995903911E-2</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="B44">
+            <v>1.9203431077271522E-2</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="B45">
+            <v>1.885405874274149E-2</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="B46">
+            <v>1.9926270390092281E-2</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="B47">
+            <v>1.8757680167698722E-2</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="B48">
+            <v>1.8829964098980797E-2</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="B49">
+            <v>1.8757680167698722E-2</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="B50">
+            <v>1.8866106064621836E-2</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="B51">
+            <v>1.8420355155049032E-2</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="B52">
+            <v>1.8480591764450764E-2</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="B53">
+            <v>1.6962629207527165E-2</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="B54">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -348,223 +660,305 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2000</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2001</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2002</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2003</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2004</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2005</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2006</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2007</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2008</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2009</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2010</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>2011</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2012</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>2013</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2014</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2015</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2016</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2017</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2018</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2019</v>
       </c>
       <c r="B21">
         <v>29336</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2020</v>
       </c>
       <c r="B22">
         <v>86249</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2021</v>
       </c>
       <c r="B23">
         <v>86779</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C23">
+        <v>86543</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2022</v>
       </c>
       <c r="B24">
         <v>90622</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C24">
+        <v>90384</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2023</v>
       </c>
       <c r="B25">
         <v>91250</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C25">
+        <v>90961</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2024</v>
       </c>
       <c r="B26">
         <v>86346</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C26">
+        <v>86088</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2025</v>
       </c>
       <c r="B27">
         <v>83520</v>
+      </c>
+      <c r="C27">
+        <f>ROUND(0.99*([1]births!$B$25*SUM([1]weekly_rates!$B$28:$B$54) + [1]births!$B$26 * SUM([1]weekly_rates!$B$2:$B$27)),0)</f>
+        <v>80649</v>
       </c>
     </row>
   </sheetData>

--- a/resources/vaccine_coverage_hun.xlsx
+++ b/resources/vaccine_coverage_hun.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CSURITA\PycharmProjects\PythonProject\counterfactual-analysis-vzv\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5214EEE-8698-40DB-A8AC-6DD2FB51E7AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D84F1000-F8F0-495D-AF38-E023E59247B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -110,285 +110,63 @@
       <sheetName val="births"/>
       <sheetName val="weekly_data"/>
       <sheetName val="weekly_rates"/>
+      <sheetName val="daily_2023"/>
+      <sheetName val="daily_2024"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="25">
-          <cell r="B25">
-            <v>85225</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="B26">
-            <v>77511</v>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="34">
+          <cell r="J34">
+            <v>7266</v>
+          </cell>
+          <cell r="K34">
+            <v>7105</v>
+          </cell>
+          <cell r="L34">
+            <v>6765</v>
+          </cell>
+          <cell r="M34">
+            <v>6609</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
-        <row r="2">
-          <cell r="B2">
-            <v>1.8914295352143218E-2</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>1.9275715008553598E-2</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4">
-            <v>1.8793822133339758E-2</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5">
-            <v>1.8842011420861143E-2</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6">
-            <v>1.9058863214707372E-2</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7">
-            <v>1.8962484639664604E-2</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8">
-            <v>1.8842011420861143E-2</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9">
-            <v>1.9131147145989447E-2</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10">
-            <v>1.9119099824109101E-2</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="B11">
-            <v>1.885405874274149E-2</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="B12">
-            <v>1.8299881936245571E-2</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13">
-            <v>1.8685396236416643E-2</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="B14">
-            <v>1.8058935498638653E-2</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="B15">
-            <v>1.7263812254535816E-2</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="B16">
-            <v>1.7468616726501698E-2</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="B17">
-            <v>1.7842083704792424E-2</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="B18">
-            <v>1.8275787292484882E-2</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="B19">
-            <v>1.8095077464279692E-2</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="B20">
-            <v>1.8589017661373875E-2</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="B21">
-            <v>1.8781774811459411E-2</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="B22">
-            <v>1.8299881936245571E-2</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="B23">
-            <v>1.8842011420861143E-2</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="B24">
-            <v>1.8902248030262872E-2</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="B25">
-            <v>1.9420282871117751E-2</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="B26">
-            <v>2.0564778449750621E-2</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="B27">
-            <v>2.0468399874707853E-2</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="B28">
-            <v>2.0456352552827507E-2</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="B29">
-            <v>2.0745488277955811E-2</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="B30">
-            <v>2.0878008818639618E-2</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="B31">
-            <v>2.0817772209237886E-2</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="B32">
-            <v>2.0661157024793389E-2</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="B33">
-            <v>2.0600920415391657E-2</v>
-          </cell>
-        </row>
+      <sheetData sheetId="4">
         <row r="34">
           <cell r="B34">
-            <v>2.0384068621545431E-2</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="B35">
-            <v>1.9950365033852974E-2</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="B36">
-            <v>1.9866033780690552E-2</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="B37">
-            <v>2.0347926655904392E-2</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="B38">
-            <v>2.0528636484109582E-2</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="B39">
-            <v>2.0805724887357539E-2</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="B40">
-            <v>2.0805724887357539E-2</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="B41">
-            <v>1.9926270390092281E-2</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="B42">
-            <v>1.9576898055562248E-2</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="B43">
-            <v>1.8938389995903911E-2</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="B44">
-            <v>1.9203431077271522E-2</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="B45">
-            <v>1.885405874274149E-2</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="B46">
-            <v>1.9926270390092281E-2</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="B47">
-            <v>1.8757680167698722E-2</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="B48">
-            <v>1.8829964098980797E-2</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="B49">
-            <v>1.8757680167698722E-2</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="B50">
-            <v>1.8866106064621836E-2</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="B51">
-            <v>1.8420355155049032E-2</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="B52">
-            <v>1.8480591764450764E-2</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="B53">
-            <v>1.6962629207527165E-2</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="B54">
-            <v>0</v>
+            <v>6670</v>
+          </cell>
+          <cell r="C34">
+            <v>6223</v>
+          </cell>
+          <cell r="D34">
+            <v>6459</v>
+          </cell>
+          <cell r="E34">
+            <v>6179</v>
+          </cell>
+          <cell r="F34">
+            <v>6350</v>
+          </cell>
+          <cell r="G34">
+            <v>6077</v>
+          </cell>
+          <cell r="H34">
+            <v>6834</v>
+          </cell>
+          <cell r="I34">
+            <v>6746</v>
+          </cell>
+          <cell r="J34">
+            <v>6731</v>
+          </cell>
+          <cell r="K34">
+            <v>6665</v>
+          </cell>
+          <cell r="L34">
+            <v>6248</v>
           </cell>
         </row>
       </sheetData>
@@ -954,11 +732,12 @@
         <v>2025</v>
       </c>
       <c r="B27">
-        <v>83520</v>
+        <f>ROUND(0.99*([1]daily_2023!$M$34+SUM([1]daily_2024!$B$34:$L$34)),0)</f>
+        <v>77013</v>
       </c>
       <c r="C27">
-        <f>ROUND(0.99*([1]births!$B$25*SUM([1]weekly_rates!$B$28:$B$54) + [1]births!$B$26 * SUM([1]weekly_rates!$B$2:$B$27)),0)</f>
-        <v>80649</v>
+        <f>ROUND(0.99*(SUM([1]daily_2023!$J$34:$M$34)+SUM([1]daily_2024!$B$34:$I$34)),0)</f>
+        <v>78490</v>
       </c>
     </row>
   </sheetData>
